--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136295919</v>
       </c>
       <c r="B6" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136296105</v>
       </c>
       <c r="B10" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136297043</v>
       </c>
       <c r="B2" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136295685</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136296227</v>
+        <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>5182</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,42 +1311,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjuvklint, Tjuvklint, Ög</t>
+          <t>Södra granstorp 101 s, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567672</v>
+        <v>567674</v>
       </c>
       <c r="R8" t="n">
-        <v>6505595</v>
+        <v>6505599</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,12 +1377,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,27 +1407,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Kråka Larsen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Kråka Larsen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136296227</t>
+          <t>https://artportalen.se/Sighting/136877203</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133374376</v>
+        <v>136296227</v>
       </c>
       <c r="B9" t="n">
-        <v>4782</v>
+        <v>5182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,46 +1435,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567688</v>
+        <v>567672</v>
       </c>
       <c r="R9" t="n">
-        <v>6505561</v>
+        <v>6505595</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,17 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På mycket gammal gran</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,34 +1508,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133374376</t>
+          <t>https://artportalen.se/Sighting/136296227</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136296105</v>
+        <v>133374376</v>
       </c>
       <c r="B10" t="n">
-        <v>58164</v>
+        <v>4782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,34 +1542,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103023</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjuvklint, Tjuvklint, Ög</t>
+          <t>Söder om Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567666</v>
+        <v>567688</v>
       </c>
       <c r="R10" t="n">
-        <v>6505600</v>
+        <v>6505561</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,12 +1605,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På mycket gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,33 +1624,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136296105</t>
+          <t>https://artportalen.se/Sighting/133374376</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133193861</v>
+        <v>136296105</v>
       </c>
       <c r="B11" t="n">
-        <v>8460</v>
+        <v>58164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567594</v>
+        <v>567666</v>
       </c>
       <c r="R11" t="n">
-        <v>6505638</v>
+        <v>6505600</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,16 +1744,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133193861</t>
+          <t>https://artportalen.se/Sighting/136296105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136297068</v>
+        <v>133193861</v>
       </c>
       <c r="B12" t="n">
-        <v>8463</v>
+        <v>8460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567596</v>
+        <v>567594</v>
       </c>
       <c r="R12" t="n">
-        <v>6505631</v>
+        <v>6505638</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1793,12 +1815,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,6 +1845,108 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133193861</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136297068</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjuvklint, Tjuvklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567596</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6505631</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136297068</t>
         </is>
@@ -1841,6 +1965,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1331,11 +1331,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17466-2026 artfynd.xlsx
+++ b/artfynd/A 17466-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136877203</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
